--- a/report/preview/data/tabular/step1/tabel_acuan_pola_RZWP3K.xlsx
+++ b/report/preview/data/tabular/step1/tabel_acuan_pola_RZWP3K.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://icrafcifor-my.sharepoint.com/personal/f_mahezs_cifor-icraf_org/Documents/Documents/GitHub/LaSPUR/data/tabular/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ICRAF\Kodingan\icraf-indonesia\LaSPUR\report\preview\data\tabular\step1\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="15" documentId="13_ncr:1_{767D952C-AD5C-40CB-83FE-211BF63B0517}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B4BC1A7-D1B7-4A62-8DA7-33BE734BDAAE}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15DF05B7-EF5E-4AD9-8641-198DA004F239}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5486" yWindow="3566" windowWidth="19748" windowHeight="11511" xr2:uid="{1BFA0940-7D81-4733-8CD1-3BF9DB729499}"/>
+    <workbookView xWindow="2580" yWindow="2580" windowWidth="17280" windowHeight="8880" xr2:uid="{1BFA0940-7D81-4733-8CD1-3BF9DB729499}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -41,9 +41,6 @@
     <t>ID</t>
   </si>
   <si>
-    <t>Prioritas</t>
-  </si>
-  <si>
     <t>RZWP3K</t>
   </si>
   <si>
@@ -114,6 +111,9 @@
   </si>
   <si>
     <t>Zona Pemanfaatan Lainnya</t>
+  </si>
+  <si>
+    <t>Acuan Pola</t>
   </si>
 </sst>
 </file>
@@ -496,270 +496,270 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{26D338C0-1963-48B6-8275-D8B0D04470E6}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="68.23046875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="68.21875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="C2">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C5">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6">
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C8">
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C9">
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C11">
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="C12">
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C13">
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="C14">
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="C15">
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="C16">
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C17">
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="C18">
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C19">
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C20">
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="C21">
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C22">
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="C23">
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C24">
         <v>0</v>
